--- a/交作业情况记录_已更新.xlsx
+++ b/交作业情况记录_已更新.xlsx
@@ -1991,7 +1991,8 @@
     <row r="44" ht="34" customHeight="1" s="7">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>说明：统计依据“作业”文件夹中各学生实际提交内容（代码 / 演示视频）核对；交作业情况单元格中括号内文字为结构性缺失提示（缺源代码、缺演示视频、多次提交等），不代表题目全部正确。</t>
+          <t>说明：统计依据“作业”文件夹中各学生实际提交内容（代码 / 演示视频）核对。
+交作业情况单元格中括号内文字为结构性缺失提示（缺源代码、缺演示视频、多次提交等），不代表题目全部正确。</t>
         </is>
       </c>
     </row>
